--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1672</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>997</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>969.5</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>969.5</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>992.5</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -62914,7 +62914,7 @@
         <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="C2720" t="n">
         <v>997</v>
@@ -62929,6 +62929,29 @@
         <v>992.5</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1448</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1006.20001220703</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>989</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>995.700012207031</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>992.5</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -62937,7 +62937,7 @@
         <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="C2721" t="n">
         <v>1006.20001220703</v>
@@ -62952,6 +62952,29 @@
         <v>992.5</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>515</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>997.700012207031</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>985</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>986</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>992.599975585938</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -62960,7 +62960,7 @@
         <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="C2722" t="n">
         <v>997.700012207031</v>
@@ -62975,6 +62975,29 @@
         <v>992.599975585938</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>888</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>992.700012207031</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>994</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>998.200012207031</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>871</v>
+        <v>1102</v>
       </c>
       <c r="C2716" t="n">
-        <v>986.299987792969</v>
+        <v>990.299987792969</v>
       </c>
       <c r="D2716" t="n">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="E2716" t="n">
-        <v>984.799987792969</v>
+        <v>988.5</v>
       </c>
       <c r="F2716" t="n">
-        <v>962.5</v>
+        <v>988.099975585938</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1440</v>
+        <v>871</v>
       </c>
       <c r="C2717" t="n">
-        <v>976.700012207031</v>
+        <v>986.299987792969</v>
       </c>
       <c r="D2717" t="n">
-        <v>965.200012207031</v>
+        <v>960</v>
       </c>
       <c r="E2717" t="n">
-        <v>968</v>
+        <v>984.799987792969</v>
       </c>
       <c r="F2717" t="n">
-        <v>970.400024414062</v>
+        <v>962.5</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>834</v>
+        <v>1440</v>
       </c>
       <c r="C2718" t="n">
-        <v>981.599975585938</v>
+        <v>976.700012207031</v>
       </c>
       <c r="D2718" t="n">
+        <v>965.200012207031</v>
+      </c>
+      <c r="E2718" t="n">
         <v>968</v>
       </c>
-      <c r="E2718" t="n">
-        <v>970</v>
-      </c>
       <c r="F2718" t="n">
-        <v>970.700012207031</v>
+        <v>970.400024414062</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>794</v>
+        <v>834</v>
       </c>
       <c r="C2719" t="n">
-        <v>975.700012207031</v>
+        <v>981.599975585938</v>
       </c>
       <c r="D2719" t="n">
-        <v>963.099975585938</v>
+        <v>968</v>
       </c>
       <c r="E2719" t="n">
-        <v>972.799987792969</v>
+        <v>970</v>
       </c>
       <c r="F2719" t="n">
-        <v>965.099975585938</v>
+        <v>970.700012207031</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1673</v>
+        <v>794</v>
       </c>
       <c r="C2720" t="n">
-        <v>997</v>
+        <v>975.700012207031</v>
       </c>
       <c r="D2720" t="n">
-        <v>969.5</v>
+        <v>963.099975585938</v>
       </c>
       <c r="E2720" t="n">
-        <v>969.5</v>
+        <v>972.799987792969</v>
       </c>
       <c r="F2720" t="n">
-        <v>992.5</v>
+        <v>965.099975585938</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,19 +62934,19 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1451</v>
+        <v>1673</v>
       </c>
       <c r="C2721" t="n">
-        <v>1006.20001220703</v>
+        <v>997</v>
       </c>
       <c r="D2721" t="n">
-        <v>989</v>
+        <v>969.5</v>
       </c>
       <c r="E2721" t="n">
-        <v>995.700012207031</v>
+        <v>969.5</v>
       </c>
       <c r="F2721" t="n">
         <v>992.5</v>
@@ -62957,22 +62957,22 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>531</v>
+        <v>1451</v>
       </c>
       <c r="C2722" t="n">
-        <v>997.700012207031</v>
+        <v>1006.20001220703</v>
       </c>
       <c r="D2722" t="n">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="E2722" t="n">
-        <v>986</v>
+        <v>995.700012207031</v>
       </c>
       <c r="F2722" t="n">
-        <v>992.599975585938</v>
+        <v>992.5</v>
       </c>
       <c r="G2722" t="s">
         <v>7</v>
@@ -62980,24 +62980,47 @@
     </row>
     <row r="2723">
       <c r="A2723" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2723" t="n">
-        <v>888</v>
+        <v>531</v>
       </c>
       <c r="C2723" t="n">
-        <v>1009</v>
+        <v>997.700012207031</v>
       </c>
       <c r="D2723" t="n">
-        <v>992.700012207031</v>
+        <v>985</v>
       </c>
       <c r="E2723" t="n">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="F2723" t="n">
-        <v>998.200012207031</v>
+        <v>992.599975585938</v>
       </c>
       <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
+        <v>754</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>998</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>1004.40002441406</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>1001.20001220703</v>
+      </c>
+      <c r="G2724" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63224,8 +63224,31 @@
       <c r="E2733" t="n">
         <v>1044.59997558594</v>
       </c>
-      <c r="F2733"/>
+      <c r="F2733" t="n">
+        <v>1047.19995117188</v>
+      </c>
       <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>1803</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>1029.80004882812</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>1025.59997558594</v>
+      </c>
+      <c r="F2734"/>
+      <c r="G2734" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1022.20001220703</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1026.80004882812</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1039.80004882812</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1021.79998779297</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63305,7 +63305,7 @@
         <v>46301.2916666667</v>
       </c>
       <c r="B2737" t="n">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="C2737" t="n">
         <v>1039.80004882812</v>
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1021.79998779297</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1032.19995117188</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1232</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1075.80004882812</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1033.19995117188</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1034.19995117188</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63328,7 +63328,7 @@
         <v>46302.2916666667</v>
       </c>
       <c r="B2738" t="n">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="C2738" t="n">
         <v>1075.80004882812</v>
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1034.19995117188</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1075.80004882812</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1087</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1068.40002441406</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1010.79998779297</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1065.59997558594</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63351,7 +63351,7 @@
         <v>46303.2916666667</v>
       </c>
       <c r="B2739" t="n">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C2739" t="n">
         <v>1068.40002441406</v>
@@ -63362,8 +63362,31 @@
       <c r="E2739" t="n">
         <v>1065.59997558594</v>
       </c>
-      <c r="F2739"/>
+      <c r="F2739" t="n">
+        <v>1020</v>
+      </c>
       <c r="G2739" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1439</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1030.40002441406</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1038.19995117188</v>
+      </c>
+      <c r="F2740"/>
+      <c r="G2740" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>3661</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>1067.40002441406</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>1056</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
